--- a/branches/dev/StructureDefinition-mii-lm-onko.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/LogicalModel/Onkologie</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-lm-onko</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Mapping: Onkologie LogicalModel oBDS Mapping</t>
   </si>
   <si>
-    <t>Onkologie</t>
+    <t>mii-lm-onko</t>
   </si>
   <si>
     <t/>
@@ -264,7 +264,7 @@
 </t>
   </si>
   <si>
-    <t>Onkologie.id</t>
+    <t>mii-lm-onko.id</t>
   </si>
   <si>
     <t>1</t>
@@ -283,7 +283,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>Onkologie.extension</t>
+    <t>mii-lm-onko.extension</t>
   </si>
   <si>
     <t>extensions
@@ -320,7 +320,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose</t>
+    <t>mii-lm-onko.Diagnose</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -336,13 +336,13 @@
     <t>5</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Diagnose.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Diagnose.modifierExtension</t>
+    <t>mii-lm-onko.Diagnose.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Diagnose.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Diagnose.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -365,7 +365,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorTumordiagnoseICDCode</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorTumordiagnoseICDCode</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -384,7 +384,7 @@
     <t>5.1</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorTumordiagnoseICDVersion</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorTumordiagnoseICDVersion</t>
   </si>
   <si>
     <t>Primärtumor Tumordiagnose ICD-Version</t>
@@ -399,7 +399,7 @@
     <t>5.2</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorTumordiagnoseText</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorTumordiagnoseText</t>
   </si>
   <si>
     <t>Primärtumor Tumordiagnose Text</t>
@@ -414,7 +414,7 @@
     <t>5.3</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorTopographieICDO</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorTopographieICDO</t>
   </si>
   <si>
     <t>Primärtumor Topographie ICD-O</t>
@@ -429,7 +429,7 @@
     <t>5.4</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorTopographieICDOVersion</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorTopographieICDOVersion</t>
   </si>
   <si>
     <t>Primärtumor Topographie ICD-O-Version</t>
@@ -444,7 +444,7 @@
     <t>5.5</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorDiagnosedatum</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorDiagnosedatum</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -463,7 +463,7 @@
     <t>5.6</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorDiagnosesicherung</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorDiagnosesicherung</t>
   </si>
   <si>
     <t>Primärtumor Diagnosesicherung</t>
@@ -478,7 +478,7 @@
     <t>5.7</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.PrimaertumorSeitenlokalisation</t>
+    <t>mii-lm-onko.Diagnose.PrimaertumorSeitenlokalisation</t>
   </si>
   <si>
     <t>Primärtumor Seitenlokalisation</t>
@@ -493,7 +493,7 @@
     <t>5.8</t>
   </si>
   <si>
-    <t>Onkologie.Diagnose.FruehereTumorerkrankungen</t>
+    <t>mii-lm-onko.Diagnose.FruehereTumorerkrankungen</t>
   </si>
   <si>
     <t xml:space="preserve">Condition
@@ -509,7 +509,7 @@
     <t>5.9</t>
   </si>
   <si>
-    <t>Onkologie.Histologie</t>
+    <t>mii-lm-onko.Histologie</t>
   </si>
   <si>
     <t>Histologie</t>
@@ -518,16 +518,16 @@
     <t>6</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Histologie.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Histologie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Histologie.TumorHistologiedatum</t>
+    <t>mii-lm-onko.Histologie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Histologie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Histologie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Histologie.TumorHistologiedatum</t>
   </si>
   <si>
     <t>Tumor Histologiedatum</t>
@@ -542,7 +542,7 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.HistologieEinsendenummer</t>
+    <t>mii-lm-onko.Histologie.HistologieEinsendenummer</t>
   </si>
   <si>
     <t>Histologie-Einsendenummer</t>
@@ -557,7 +557,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.MorphologieCode</t>
+    <t>mii-lm-onko.Histologie.MorphologieCode</t>
   </si>
   <si>
     <t>Morphologie-Code</t>
@@ -572,7 +572,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.MorphologieICDOBlueBookVersion</t>
+    <t>mii-lm-onko.Histologie.MorphologieICDOBlueBookVersion</t>
   </si>
   <si>
     <t>Morphologie ICD-O/Blue Book Version</t>
@@ -587,7 +587,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.MorphologieFreitext</t>
+    <t>mii-lm-onko.Histologie.MorphologieFreitext</t>
   </si>
   <si>
     <t>Morphologie-Freitext</t>
@@ -599,7 +599,7 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.Grading</t>
+    <t>mii-lm-onko.Histologie.Grading</t>
   </si>
   <si>
     <t>Grading</t>
@@ -614,7 +614,7 @@
     <t>6.6</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.AnzahlUntersuchteLymphknoten</t>
+    <t>mii-lm-onko.Histologie.AnzahlUntersuchteLymphknoten</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
@@ -633,7 +633,7 @@
     <t>6.7</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.AnzahlBefalleneLymphknoten</t>
+    <t>mii-lm-onko.Histologie.AnzahlBefalleneLymphknoten</t>
   </si>
   <si>
     <t>Anzahl der befallenen Lymphknoten</t>
@@ -648,7 +648,7 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.AnzahlUntersuchteSentinelLymphknoten</t>
+    <t>mii-lm-onko.Histologie.AnzahlUntersuchteSentinelLymphknoten</t>
   </si>
   <si>
     <t>Anzahl der untersuchten Sentinel-Lymphknoten</t>
@@ -663,7 +663,7 @@
     <t>6.9</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.AnzahlBefalleneSentinelLymphknoten</t>
+    <t>mii-lm-onko.Histologie.AnzahlBefalleneSentinelLymphknoten</t>
   </si>
   <si>
     <t>Anzahl der befallenen Sentinel-Lymphknoten</t>
@@ -678,7 +678,7 @@
     <t>6.10</t>
   </si>
   <si>
-    <t>Onkologie.Histologie.Befund</t>
+    <t>mii-lm-onko.Histologie.Befund</t>
   </si>
   <si>
     <t>Befund</t>
@@ -693,7 +693,7 @@
     <t>6.11</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation</t>
+    <t>mii-lm-onko.TNMKlassifikation</t>
   </si>
   <si>
     <t>TNM-Klassifikation</t>
@@ -702,16 +702,16 @@
     <t>8</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.id</t>
-  </si>
-  <si>
-    <t>Onkologie.TNMKlassifikation.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.TNMKlassifikation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.TNMKlassifikation.TNMDatum</t>
+    <t>mii-lm-onko.TNMKlassifikation.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.TNMKlassifikation.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.TNMKlassifikation.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.TNMKlassifikation.TNMDatum</t>
   </si>
   <si>
     <t>TNM Datum</t>
@@ -726,7 +726,7 @@
     <t>8.1</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMVersion</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMVersion</t>
   </si>
   <si>
     <t>TNM Version</t>
@@ -741,7 +741,7 @@
     <t>8.2</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMySymbol</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMySymbol</t>
   </si>
   <si>
     <t>TNM y-Symbol</t>
@@ -760,7 +760,7 @@
     <t>8.3</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMrSymbol</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMrSymbol</t>
   </si>
   <si>
     <t>TNM r-Symbol</t>
@@ -776,7 +776,7 @@
     <t>8.4</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMaSymbol</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMaSymbol</t>
   </si>
   <si>
     <t>TNM a-Symbol</t>
@@ -792,7 +792,7 @@
     <t>8.5</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMcpuPraefixT</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMcpuPraefixT</t>
   </si>
   <si>
     <t>TNM c/p-Präfix T</t>
@@ -807,7 +807,7 @@
     <t>8.6</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMcpuPraefixN</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMcpuPraefixN</t>
   </si>
   <si>
     <t>TNM c/p-Präfix N</t>
@@ -816,7 +816,7 @@
     <t>8.7</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMcpuPraefixM</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMcpuPraefixM</t>
   </si>
   <si>
     <t>TNM c/p-Präfix M</t>
@@ -825,7 +825,7 @@
     <t>8.8</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMTKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMTKategorie</t>
   </si>
   <si>
     <t>TNM T-Kategorie</t>
@@ -837,7 +837,7 @@
     <t>8.9</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMmSymbol</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMmSymbol</t>
   </si>
   <si>
     <t>TNM m-Symbol</t>
@@ -849,7 +849,7 @@
     <t>8.10</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMMKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMMKategorie</t>
   </si>
   <si>
     <t>TNM M-Kategorie</t>
@@ -861,7 +861,7 @@
     <t>8.12</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMNKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMNKategorie</t>
   </si>
   <si>
     <t>TNM N-Kategorie</t>
@@ -873,7 +873,7 @@
     <t>8.11</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMLKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMLKategorie</t>
   </si>
   <si>
     <t>TNM L-Kategorie</t>
@@ -889,7 +889,7 @@
     <t>8.13</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMVKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMVKategorie</t>
   </si>
   <si>
     <t>TNM V-Kategorie</t>
@@ -905,7 +905,7 @@
     <t>8.14</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMPnKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMPnKategorie</t>
   </si>
   <si>
     <t>TNM Pn-Kategorie</t>
@@ -921,7 +921,7 @@
     <t>8.15</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.TNMSKategorie</t>
+    <t>mii-lm-onko.TNMKlassifikation.TNMSKategorie</t>
   </si>
   <si>
     <t>TNM S-Kategorie</t>
@@ -937,7 +937,7 @@
     <t>8.16</t>
   </si>
   <si>
-    <t>Onkologie.TNMKlassifikation.UICCStadium</t>
+    <t>mii-lm-onko.TNMKlassifikation.UICCStadium</t>
   </si>
   <si>
     <t>UICC Stadium</t>
@@ -949,7 +949,7 @@
     <t>8.17</t>
   </si>
   <si>
-    <t>Onkologie.WeitereKlassifikationen</t>
+    <t>mii-lm-onko.WeitereKlassifikationen</t>
   </si>
   <si>
     <t>Observation</t>
@@ -958,16 +958,16 @@
     <t>9</t>
   </si>
   <si>
-    <t>Onkologie.WeitereKlassifikationen.id</t>
-  </si>
-  <si>
-    <t>Onkologie.WeitereKlassifikationen.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.WeitereKlassifikationen.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.WeitereKlassifikationen.WeitereKlassifikationDatum</t>
+    <t>mii-lm-onko.WeitereKlassifikationen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.WeitereKlassifikationen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.WeitereKlassifikationen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.WeitereKlassifikationen.WeitereKlassifikationDatum</t>
   </si>
   <si>
     <t xml:space="preserve">date
@@ -983,7 +983,7 @@
     <t>9.1</t>
   </si>
   <si>
-    <t>Onkologie.WeitereKlassifikationen.WeitereKlassifikationName</t>
+    <t>mii-lm-onko.WeitereKlassifikationen.WeitereKlassifikationName</t>
   </si>
   <si>
     <t>Hämatoonkologische und sonstige Klassifikationen Name</t>
@@ -998,7 +998,7 @@
     <t>9.2</t>
   </si>
   <si>
-    <t>Onkologie.WeitereKlassifikationen.WeitereKlassifikationEinstufung</t>
+    <t>mii-lm-onko.WeitereKlassifikationen.WeitereKlassifikationEinstufung</t>
   </si>
   <si>
     <t>Hämatoonkologische und sonstige Klassifikationen Einstufung</t>
@@ -1013,7 +1013,7 @@
     <t>9.3</t>
   </si>
   <si>
-    <t>Onkologie.Residualstatus</t>
+    <t>mii-lm-onko.Residualstatus</t>
   </si>
   <si>
     <t>Residualstatus</t>
@@ -1022,16 +1022,16 @@
     <t>10</t>
   </si>
   <si>
-    <t>Onkologie.Residualstatus.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Residualstatus.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Residualstatus.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Residualstatus.LokalerResidualstatus</t>
+    <t>mii-lm-onko.Residualstatus.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Residualstatus.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Residualstatus.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Residualstatus.LokalerResidualstatus</t>
   </si>
   <si>
     <t>Beurteilung des lokalen Residualstatus nach Abschluss der Operation</t>
@@ -1046,7 +1046,7 @@
     <t>10.1</t>
   </si>
   <si>
-    <t>Onkologie.Residualstatus.GlobalerResidualstatus</t>
+    <t>mii-lm-onko.Residualstatus.GlobalerResidualstatus</t>
   </si>
   <si>
     <t>Gesamtbeurteilung des Residualstatus</t>
@@ -1058,7 +1058,7 @@
     <t>10.2</t>
   </si>
   <si>
-    <t>Onkologie.Fernmetastasen</t>
+    <t>mii-lm-onko.Fernmetastasen</t>
   </si>
   <si>
     <t>Fernmetastasen</t>
@@ -1067,16 +1067,16 @@
     <t>11</t>
   </si>
   <si>
-    <t>Onkologie.Fernmetastasen.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Fernmetastasen.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Fernmetastasen.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Fernmetastasen.LokalisationFernmetastase</t>
+    <t>mii-lm-onko.Fernmetastasen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Fernmetastasen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Fernmetastasen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Fernmetastasen.LokalisationFernmetastase</t>
   </si>
   <si>
     <t>Lokalisation von Fernmetastase(n)</t>
@@ -1091,7 +1091,7 @@
     <t>11.1</t>
   </si>
   <si>
-    <t>Onkologie.Fernmetastasen.DatumFernmetase</t>
+    <t>mii-lm-onko.Fernmetastasen.DatumFernmetase</t>
   </si>
   <si>
     <t>Datum der diagnostischen Sicherung von Fernmetastasen</t>
@@ -1103,7 +1103,7 @@
     <t>11.2</t>
   </si>
   <si>
-    <t>Onkologie.AllgemeinerLeistungszustand</t>
+    <t>mii-lm-onko.AllgemeinerLeistungszustand</t>
   </si>
   <si>
     <t>Allgemeiner Leistungszustand</t>
@@ -1112,16 +1112,16 @@
     <t>12</t>
   </si>
   <si>
-    <t>Onkologie.AllgemeinerLeistungszustand.id</t>
-  </si>
-  <si>
-    <t>Onkologie.AllgemeinerLeistungszustand.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.AllgemeinerLeistungszustand.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.AllgemeinerLeistungszustand.ECOGKarnofsky</t>
+    <t>mii-lm-onko.AllgemeinerLeistungszustand.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.AllgemeinerLeistungszustand.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.AllgemeinerLeistungszustand.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.AllgemeinerLeistungszustand.ECOGKarnofsky</t>
   </si>
   <si>
     <t>ECOG oder Karnofsky</t>
@@ -1130,7 +1130,7 @@
     <t>12.1</t>
   </si>
   <si>
-    <t>Onkologie.Operation</t>
+    <t>mii-lm-onko.Operation</t>
   </si>
   <si>
     <t>Operation</t>
@@ -1139,16 +1139,16 @@
     <t>13</t>
   </si>
   <si>
-    <t>Onkologie.Operation.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Operation.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Operation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Operation.OPIntention</t>
+    <t>mii-lm-onko.Operation.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Operation.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Operation.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Operation.OPIntention</t>
   </si>
   <si>
     <t>Intention</t>
@@ -1163,7 +1163,7 @@
     <t>13.1</t>
   </si>
   <si>
-    <t>Onkologie.Operation.OPDatum</t>
+    <t>mii-lm-onko.Operation.OPDatum</t>
   </si>
   <si>
     <t>OP Datum</t>
@@ -1178,7 +1178,7 @@
     <t>13.2</t>
   </si>
   <si>
-    <t>Onkologie.Operation.OPSCode</t>
+    <t>mii-lm-onko.Operation.OPSCode</t>
   </si>
   <si>
     <t>OPS Code</t>
@@ -1193,7 +1193,7 @@
     <t>13.3</t>
   </si>
   <si>
-    <t>Onkologie.Operation.OPSVersion</t>
+    <t>mii-lm-onko.Operation.OPSVersion</t>
   </si>
   <si>
     <t>OPS Version</t>
@@ -1208,7 +1208,7 @@
     <t>13.4</t>
   </si>
   <si>
-    <t>Onkologie.Operation.OPKomplikation</t>
+    <t>mii-lm-onko.Operation.OPKomplikation</t>
   </si>
   <si>
     <t>OP Komplikationen</t>
@@ -1223,7 +1223,7 @@
     <t>13.5</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie</t>
+    <t>mii-lm-onko.Strahlentherapie</t>
   </si>
   <si>
     <t>Strahlentherapie</t>
@@ -1232,16 +1232,16 @@
     <t>14</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieIntention</t>
+    <t>mii-lm-onko.Strahlentherapie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieIntention</t>
   </si>
   <si>
     <t>Intention der Strahlentherapie</t>
@@ -1256,7 +1256,7 @@
     <t>14.1</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieStellung</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieStellung</t>
   </si>
   <si>
     <t>Strahlentherapie Stellung zu operativer Therapie</t>
@@ -1271,7 +1271,7 @@
     <t>14.2</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieEndeGrund</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieEndeGrund</t>
   </si>
   <si>
     <t>Strahlentherapie Ende Grund</t>
@@ -1286,7 +1286,7 @@
     <t>14.13</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung</t>
   </si>
   <si>
     <t>Bestrahlung</t>
@@ -1301,16 +1301,16 @@
     <t>14.3-14.12</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieZielgebiet</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieZielgebiet</t>
   </si>
   <si>
     <t>Strahlentherapie Zielgebiet</t>
@@ -1325,7 +1325,7 @@
     <t>14.3</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieSeiteZielgebiet</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieSeiteZielgebiet</t>
   </si>
   <si>
     <t>Strahlentherapie Seite Zielgebiet</t>
@@ -1340,7 +1340,7 @@
     <t>14.4</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieBeginn</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieBeginn</t>
   </si>
   <si>
     <t>Strahlentherapie Beginn</t>
@@ -1355,7 +1355,7 @@
     <t>14.5</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEnde</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEnde</t>
   </si>
   <si>
     <t>Strahlentherapie Ende</t>
@@ -1370,7 +1370,7 @@
     <t>14.6</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieApplikationsart</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieApplikationsart</t>
   </si>
   <si>
     <t>Strahlentherapie Applikationsart</t>
@@ -1385,7 +1385,7 @@
     <t>14.7</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieStrahlenart</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieStrahlenart</t>
   </si>
   <si>
     <t>Strahlenart</t>
@@ -1400,7 +1400,7 @@
     <t>14.8</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieGesamtdosis</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieGesamtdosis</t>
   </si>
   <si>
     <t>Strahlentherapie Gesamtdosis</t>
@@ -1415,7 +1415,7 @@
     <t>14.9</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEinzeldosis</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEinzeldosis</t>
   </si>
   <si>
     <t>Strahlentherapie Einzeldosis</t>
@@ -1430,7 +1430,7 @@
     <t>14.10</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEinheit</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieEinheit</t>
   </si>
   <si>
     <t>Strahlentherapie Einheit</t>
@@ -1445,7 +1445,7 @@
     <t>14.11</t>
   </si>
   <si>
-    <t>Onkologie.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieBoost</t>
+    <t>mii-lm-onko.Strahlentherapie.StrahlentherapieBestrahlung.StrahlentherapieBoost</t>
   </si>
   <si>
     <t>Boost</t>
@@ -1460,7 +1460,7 @@
     <t>14.12</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie</t>
+    <t>mii-lm-onko.SystemischeTherapie</t>
   </si>
   <si>
     <t>Systemische Therapie</t>
@@ -1469,16 +1469,16 @@
     <t>16</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.id</t>
-  </si>
-  <si>
-    <t>Onkologie.SystemischeTherapie.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.SystemischeTherapie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieIntention</t>
+    <t>mii-lm-onko.SystemischeTherapie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.SystemischeTherapie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.SystemischeTherapie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieIntention</t>
   </si>
   <si>
     <t>Intention der systemischen Therapie</t>
@@ -1487,7 +1487,7 @@
     <t>16.1</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieStellung</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieStellung</t>
   </si>
   <si>
     <t>Systemische Therapie Stellung zu operativer Therapie</t>
@@ -1499,7 +1499,7 @@
     <t>16.2</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieArtTherapie</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieArtTherapie</t>
   </si>
   <si>
     <t>Art der systemischen oder abwartenden Therapie</t>
@@ -1511,7 +1511,7 @@
     <t>16.3</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieProtokoll</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieProtokoll</t>
   </si>
   <si>
     <t>Systemische Therapie Protokoll</t>
@@ -1526,7 +1526,7 @@
     <t>16.4</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieSubstanz</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieSubstanz</t>
   </si>
   <si>
     <t>Systemische Therapie Substanz</t>
@@ -1541,7 +1541,7 @@
     <t>16.6</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieBeginn</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieBeginn</t>
   </si>
   <si>
     <t>Systemische Therapie Beginn</t>
@@ -1553,7 +1553,7 @@
     <t>16.5</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieEnde</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieEnde</t>
   </si>
   <si>
     <t>Systemische Therapie Ende Grund</t>
@@ -1565,7 +1565,7 @@
     <t>16.8</t>
   </si>
   <si>
-    <t>Onkologie.SystemischeTherapie.SystemischeTherapieEndeGrund</t>
+    <t>mii-lm-onko.SystemischeTherapie.SystemischeTherapieEndeGrund</t>
   </si>
   <si>
     <t>Systemische Therapie Ende</t>
@@ -1577,7 +1577,7 @@
     <t>16.7</t>
   </si>
   <si>
-    <t>Onkologie.Nebenwirkungen</t>
+    <t>mii-lm-onko.Nebenwirkungen</t>
   </si>
   <si>
     <t>Nebenwirkungen</t>
@@ -1586,16 +1586,16 @@
     <t>15</t>
   </si>
   <si>
-    <t>Onkologie.Nebenwirkungen.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Nebenwirkungen.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Nebenwirkungen.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Nebenwirkungen.NebenwirkungenCTCAEGrad</t>
+    <t>mii-lm-onko.Nebenwirkungen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Nebenwirkungen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Nebenwirkungen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Nebenwirkungen.NebenwirkungenCTCAEGrad</t>
   </si>
   <si>
     <t>Nebenwirkungen nach CTCAE-Grad</t>
@@ -1610,7 +1610,7 @@
     <t>15.1</t>
   </si>
   <si>
-    <t>Onkologie.Nebenwirkungen.NebenwirkungenCTCAEArt</t>
+    <t>mii-lm-onko.Nebenwirkungen.NebenwirkungenCTCAEArt</t>
   </si>
   <si>
     <t>Nebenwirkungen nach CTCAE Art</t>
@@ -1625,7 +1625,7 @@
     <t>15.2</t>
   </si>
   <si>
-    <t>Onkologie.Nebenwirkungen.NebenwirkungenCTCAEVersion</t>
+    <t>mii-lm-onko.Nebenwirkungen.NebenwirkungenCTCAEVersion</t>
   </si>
   <si>
     <t>Nebenwirkungen nach CTCAE Version</t>
@@ -1640,7 +1640,7 @@
     <t>15.3</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf</t>
+    <t>mii-lm-onko.Verlauf</t>
   </si>
   <si>
     <t>Verlauf</t>
@@ -1649,16 +1649,16 @@
     <t>17</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Verlauf.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Verlauf.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Verlauf.VerlaufDatum</t>
+    <t>mii-lm-onko.Verlauf.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Verlauf.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Verlauf.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Verlauf.VerlaufDatum</t>
   </si>
   <si>
     <t>Untersuchungsdatum Verlauf</t>
@@ -1670,7 +1670,7 @@
     <t>17.1</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf.VerlaufBeurteilungTumorstatus</t>
+    <t>mii-lm-onko.Verlauf.VerlaufBeurteilungTumorstatus</t>
   </si>
   <si>
     <t>Gesamtbeurteilung des Tumorstatus</t>
@@ -1682,7 +1682,7 @@
     <t>17.2</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf.VerlaufTumorstatusPrimaertumor</t>
+    <t>mii-lm-onko.Verlauf.VerlaufTumorstatusPrimaertumor</t>
   </si>
   <si>
     <t>Tumorstatus Primärtumor</t>
@@ -1694,7 +1694,7 @@
     <t>17.3</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf.VerlaufTumorstatusLymphknoten</t>
+    <t>mii-lm-onko.Verlauf.VerlaufTumorstatusLymphknoten</t>
   </si>
   <si>
     <t>Tumorstatus Lymphknoten</t>
@@ -1706,7 +1706,7 @@
     <t>17.4</t>
   </si>
   <si>
-    <t>Onkologie.Verlauf.VerlaufTumorstatusMetastasen</t>
+    <t>mii-lm-onko.Verlauf.VerlaufTumorstatusMetastasen</t>
   </si>
   <si>
     <t>Tumorstatus Fernmetastasen</t>
@@ -1718,7 +1718,7 @@
     <t>17.5</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz</t>
+    <t>mii-lm-onko.Tumorkonferenz</t>
   </si>
   <si>
     <t>Tumorkonferenz und Therapieempfehlung</t>
@@ -1727,16 +1727,16 @@
     <t>18, 19</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Tumorkonferenz.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Tumorkonferenz.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieplanungDatum</t>
+    <t>mii-lm-onko.Tumorkonferenz.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tumorkonferenz.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tumorkonferenz.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieplanungDatum</t>
   </si>
   <si>
     <t>Tumorkonferenz Therapieplanung Datum</t>
@@ -1751,7 +1751,7 @@
     <t>18.1</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieplanungTyp</t>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieplanungTyp</t>
   </si>
   <si>
     <t>Tumorkonferenz Therapieplanung Typ</t>
@@ -1766,7 +1766,7 @@
     <t>18.2</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieempfehlungTyp</t>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieempfehlungTyp</t>
   </si>
   <si>
     <t>Tumorkonferenz Therapieempfehlung Typ</t>
@@ -1781,7 +1781,7 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieempfehlungProtokoll</t>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieempfehlungProtokoll</t>
   </si>
   <si>
     <t>Tumorkonferenz Therapieempfehlung Protokoll</t>
@@ -1796,7 +1796,7 @@
     <t>19.1 (Erweiterung)</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieempfehlungMedikation</t>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieempfehlungMedikation</t>
   </si>
   <si>
     <t>Tumorkonferenz Therapieempfehlung Medikation</t>
@@ -1808,7 +1808,7 @@
     <t>MedicationRequest.medicationCodeableConcept (referenced from RequestGroup.action.action.resource)</t>
   </si>
   <si>
-    <t>Onkologie.Tumorkonferenz.TumorkonferenzTherapieAbweichungPatientenwunsch</t>
+    <t>mii-lm-onko.Tumorkonferenz.TumorkonferenzTherapieAbweichungPatientenwunsch</t>
   </si>
   <si>
     <t>Tumorkonferenz/Therapieempfehlung Therapieabweichung auf Wunsch des Patienten</t>
@@ -1823,7 +1823,7 @@
     <t>19.2</t>
   </si>
   <si>
-    <t>Onkologie.Tod</t>
+    <t>mii-lm-onko.Tod</t>
   </si>
   <si>
     <t>Tod</t>
@@ -1832,16 +1832,16 @@
     <t>20</t>
   </si>
   <si>
-    <t>Onkologie.Tod.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Tod.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Tod.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Tod.Sterbedatum</t>
+    <t>mii-lm-onko.Tod.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tod.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tod.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Tod.Sterbedatum</t>
   </si>
   <si>
     <t>Sterbedatum</t>
@@ -1853,7 +1853,7 @@
     <t>20.1</t>
   </si>
   <si>
-    <t>Onkologie.Tod.TodTumorbedingt</t>
+    <t>mii-lm-onko.Tod.TodTumorbedingt</t>
   </si>
   <si>
     <t>Tod tumorbedingt</t>
@@ -1868,7 +1868,7 @@
     <t>20.2</t>
   </si>
   <si>
-    <t>Onkologie.Tod.TodesursacheICD</t>
+    <t>mii-lm-onko.Tod.TodesursacheICD</t>
   </si>
   <si>
     <t>Todesursache ICD</t>
@@ -1880,7 +1880,7 @@
     <t>20.3</t>
   </si>
   <si>
-    <t>Onkologie.Tod.TodesursacheICDVersion</t>
+    <t>mii-lm-onko.Tod.TodesursacheICDVersion</t>
   </si>
   <si>
     <t>Todesursache ICD Version</t>
@@ -1895,7 +1895,7 @@
     <t>20.4</t>
   </si>
   <si>
-    <t>Onkologie.GenetischeVariante</t>
+    <t>mii-lm-onko.GenetischeVariante</t>
   </si>
   <si>
     <t>Genetische Variante</t>
@@ -1904,16 +1904,16 @@
     <t>23</t>
   </si>
   <si>
-    <t>Onkologie.GenetischeVariante.id</t>
-  </si>
-  <si>
-    <t>Onkologie.GenetischeVariante.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.GenetischeVariante.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.GenetischeVariante.GenetischeVarianteName</t>
+    <t>mii-lm-onko.GenetischeVariante.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.GenetischeVariante.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.GenetischeVariante.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.GenetischeVariante.GenetischeVarianteName</t>
   </si>
   <si>
     <t>Genetische Variante Name</t>
@@ -1928,7 +1928,7 @@
     <t>23.1</t>
   </si>
   <si>
-    <t>Onkologie.GenetischeVariante.GenetischeVarianteAuspraegung</t>
+    <t>mii-lm-onko.GenetischeVariante.GenetischeVarianteAuspraegung</t>
   </si>
   <si>
     <t>Genetische Variante Ausprägung</t>
@@ -1943,7 +1943,7 @@
     <t>23.2</t>
   </si>
   <si>
-    <t>Onkologie.Studienteilnahme</t>
+    <t>mii-lm-onko.Studienteilnahme</t>
   </si>
   <si>
     <t>Studienteilnahme</t>
@@ -1952,16 +1952,16 @@
     <t>24</t>
   </si>
   <si>
-    <t>Onkologie.Studienteilnahme.id</t>
-  </si>
-  <si>
-    <t>Onkologie.Studienteilnahme.extension</t>
-  </si>
-  <si>
-    <t>Onkologie.Studienteilnahme.modifierExtension</t>
-  </si>
-  <si>
-    <t>Onkologie.Studienteilnahme.StudienteilnahmeStatus</t>
+    <t>mii-lm-onko.Studienteilnahme.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Studienteilnahme.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Studienteilnahme.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko.Studienteilnahme.StudienteilnahmeStatus</t>
   </si>
   <si>
     <t>Studienteilnahme Status</t>
@@ -1973,7 +1973,7 @@
     <t>24.1</t>
   </si>
   <si>
-    <t>Onkologie.Studienteilnahme.StudienteilnahmeDatum</t>
+    <t>mii-lm-onko.Studienteilnahme.StudienteilnahmeDatum</t>
   </si>
   <si>
     <t>Studienteilnahme Datum</t>
@@ -1985,7 +1985,7 @@
     <t>24.2</t>
   </si>
   <si>
-    <t>Onkologie.Studienteilnahme.StudienteilnahmeStudienreferenz</t>
+    <t>mii-lm-onko.Studienteilnahme.StudienteilnahmeStudienreferenz</t>
   </si>
   <si>
     <t xml:space="preserve">Reference
@@ -2308,8 +2308,8 @@
   <dimension ref="A1:AL166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.32421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="71.32421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.75390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="72.75390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2339,7 +2339,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="71.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="72.75390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/branches/dev/StructureDefinition-mii-lm-onko.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
